--- a/Shopee_Dataset/1_Structured_Data/shops_master.xlsx
+++ b/Shopee_Dataset/1_Structured_Data/shops_master.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shops_master" sheetId="1" r:id="Rcc787979f85e414b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R16cb604df9cc4fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shops_master" sheetId="1" r:id="Rfb2ac8dd30d24de5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R07d7a2c291a64f07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,12 +26,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -46,7 +51,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -76,6 +81,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -279,59 +287,59 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="49" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="29" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="10" t="str">
+      <x:c r="A1" s="14" t="str">
         <x:v>Shop_ID</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="14" t="str">
         <x:v>Shop_Name</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
+      <x:c r="C1" s="14" t="str">
         <x:v>Shop_type</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="str">
+      <x:c r="D1" s="14" t="str">
         <x:v>Years_Active</x:v>
       </x:c>
-      <x:c r="E1" s="10" t="str">
+      <x:c r="E1" s="14" t="str">
         <x:v>Is_Online_Now</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="str">
+      <x:c r="F1" s="14" t="str">
         <x:v>Total_Products</x:v>
       </x:c>
-      <x:c r="G1" s="10" t="str">
+      <x:c r="G1" s="14" t="str">
         <x:v>Follower_Count_k</x:v>
       </x:c>
-      <x:c r="H1" s="10" t="str">
+      <x:c r="H1" s="14" t="str">
         <x:v>Rating_Average</x:v>
       </x:c>
-      <x:c r="I1" s="10" t="str">
+      <x:c r="I1" s="14" t="str">
         <x:v>Total_Ratings_k</x:v>
       </x:c>
-      <x:c r="J1" s="10" t="str">
+      <x:c r="J1" s="14" t="str">
         <x:v>Chat_Response_Rate_pct</x:v>
       </x:c>
-      <x:c r="K1" s="10" t="str">
+      <x:c r="K1" s="14" t="str">
         <x:v>Has_Voucher</x:v>
       </x:c>
-      <x:c r="L1" s="10" t="str">
+      <x:c r="L1" s="14" t="str">
         <x:v>Target_Label</x:v>
       </x:c>
-      <x:c r="M1" s="10" t="str">
+      <x:c r="M1" s="14" t="str">
         <x:v>Time_Collected</x:v>
       </x:c>
     </x:row>
@@ -345,20 +353,22 @@
       <x:c r="C2" s="11" t="str">
         <x:v>Shopee Mall</x:v>
       </x:c>
-      <x:c r="D2" s="11"/>
-      <x:c r="E2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="D2" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E2" s="11"/>
       <x:c r="F2" s="11" t="n">
-        <x:v>11400</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>104.5</x:v>
+        <x:v>104.7</x:v>
       </x:c>
       <x:c r="H2" s="11" t="n">
         <x:v>4.8</x:v>
       </x:c>
-      <x:c r="I2" s="11"/>
+      <x:c r="I2" s="11" t="n">
+        <x:v>8.9</x:v>
+      </x:c>
       <x:c r="J2" s="11" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -367,7 +377,7 @@
       </x:c>
       <x:c r="L2" s="11"/>
       <x:c r="M2" s="11" t="str">
-        <x:v>20260921</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -380,29 +390,31 @@
       <x:c r="C3" s="11" t="str">
         <x:v>Shopee Mall</x:v>
       </x:c>
-      <x:c r="D3" s="11"/>
-      <x:c r="E3" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="D3" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="11"/>
       <x:c r="F3" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>129.8</x:v>
+        <x:v>129.9</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
         <x:v>4.9</x:v>
       </x:c>
-      <x:c r="I3" s="11"/>
+      <x:c r="I3" s="11" t="n">
+        <x:v>108.2</x:v>
+      </x:c>
       <x:c r="J3" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="L3" s="11"/>
       <x:c r="M3" s="11" t="str">
-        <x:v>20260921</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -415,27 +427,453 @@
       <x:c r="C4" s="11" t="str">
         <x:v>Shopee Mall</x:v>
       </x:c>
-      <x:c r="D4" s="11"/>
-      <x:c r="E4" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="D4" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E4" s="11"/>
       <x:c r="F4" s="11" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>524.6</x:v>
+        <x:v>525.1</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
         <x:v>4.9</x:v>
       </x:c>
-      <x:c r="I4" s="11"/>
+      <x:c r="I4" s="11" t="n">
+        <x:v>132.4</x:v>
+      </x:c>
       <x:c r="J4" s="11" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K4" s="11"/>
       <x:c r="L4" s="11"/>
       <x:c r="M4" s="11" t="str">
-        <x:v>20260921</x:v>
+        <x:v>2026-09-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>01_004</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Hoàng Phúc International</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G5" t="n">
+        <x:v>181.3</x:v>
+      </x:c>
+      <x:c r="H5" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>55.6</x:v>
+      </x:c>
+      <x:c r="J5" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5"/>
+      <x:c r="M5" t="str">
+        <x:v>2026-09-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>01_005</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Lock&amp;Lock Official Store (Cửa hàng chính hãng)</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6" t="n">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="G6" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>711.8</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L6"/>
+      <x:c r="M6" t="str">
+        <x:v>2026-09-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>01_006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Ugreen Official Shop</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="G7" t="n">
+        <x:v>694.9</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>279.6</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+      <x:c r="M7" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>01_007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>BAMA.BAG</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>330.2</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>47.2</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+      <x:c r="M8" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>01_008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>SMART HOUSEHOLD</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>8.9</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+      <x:c r="M9" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>01_009</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Gia Dụng Việt_123</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Shop thường</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>10.2</x:v>
+      </x:c>
+      <x:c r="H10" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J10" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+      <x:c r="M10" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>01_010</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Shop Mẹ Gold1</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Shop thường</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11" t="n">
+        <x:v>762</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>131.1</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>471.8</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+      <x:c r="M11" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>01_011</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Deli Official Store</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="H12" t="n">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="J12" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+      <x:c r="M12" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>01_012</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>TECHZONE AUDIO</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E13"/>
+      <x:c r="F13" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" t="n">
+        <x:v>6.1</x:v>
+      </x:c>
+      <x:c r="H13" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="I13" t="n">
+        <x:v>9.7</x:v>
+      </x:c>
+      <x:c r="J13" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+      <x:c r="M13" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>01_013</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>CHUYÊN LOA HOT TREND</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Shopee Mall</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G14" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H14" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="I14" t="n">
+        <x:v>6.4</x:v>
+      </x:c>
+      <x:c r="J14" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+      <x:c r="M14" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>01_014</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>MINH PHÁT PRINTING</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Shop thường</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E15"/>
+      <x:c r="F15" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G15" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H15" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="I15" t="n">
+        <x:v>50.6</x:v>
+      </x:c>
+      <x:c r="J15" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+      <x:c r="M15" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>01_015</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Topick Global</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Shop thường</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16" t="n">
+        <x:v>324300</x:v>
+      </x:c>
+      <x:c r="G16" t="n">
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="H16" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>7300</x:v>
+      </x:c>
+      <x:c r="J16" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+      <x:c r="M16" t="str">
+        <x:v>2026-09-28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -450,7 +888,7 @@
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="80" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="90" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -475,10 +913,10 @@
         <x:v>https://shopee.vn/maisononline</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>https://shopee.vn/CONVERSE-Gi%C3%A0y-sneakers-unisex-c%E1%BB%95-th%E1%BA%A5p-Chuck-Taylor-All-Star-1970s-162063C-0000_YELLOW-i.364616598.26126035970</x:v>
+        <x:v>https://shopee.vn/product/364616598/26826031139</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Rating/follower lấy từ shop page; product count 11.4K và chat response 87% từ product page. Years_Active và Total_Ratings_k không hiển thị trong bản index công khai.</x:v>
+        <x:v>Quan sát trên trang sản phẩm ngày 2026-09-27. 11,6k sản phẩm, 104,7k follower, 8,9k ratings; Years_Active làm tròn từ Joined 6 years ago; online để trống vì thay đổi theo phút.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -489,10 +927,10 @@
         <x:v>https://shopee.vn/astromazing</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>https://shopee.vn/-Ng%C3%B2i-ch%C3%ADnh-h%C3%A3ng-%C4%90%E1%BA%A7u-ng%C3%B2i-b%C3%BAt-thay-th%E1%BA%BF-cao-c%E1%BA%A5p-AstroMazing-cho-b%C3%BAt-Apple-Pencil-1-v%C3%A0-2-i.320823232.8329904805</x:v>
+        <x:v>https://shopee.vn/product/320823232/8329904805</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Rating/follower lấy từ shop page; product count/chat response lấy từ product page công khai. Years_Active và Total_Ratings_k không hiển thị trong bản index công khai.</x:v>
+        <x:v>Quan sát trên trang sản phẩm ngày 2026-09-27. 98 sản phẩm, 129,9k follower, 108,2k ratings; Joined 6 years ago; online để trống.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -503,10 +941,178 @@
         <x:v>https://shopee.vn/camelia_vn</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>https://shopee.vn/Balo-CAMELIA-BRAND%C2%AE-Global-Backpack-i.233235070.7618653327</x:v>
+        <x:v>https://shopee.vn/product/233235070/7618653327</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Rating/follower lấy từ shop page; product count 90 và chat response 100% từ product page. Years_Active và Total_Ratings_k không hiển thị trong bản index công khai.</x:v>
+        <x:v>Quan sát trên trang sản phẩm ngày 2026-09-27. 90 sản phẩm, 525,1k follower, 132,4k ratings; Joined 7 years ago; Has_Voucher chưa xác minh.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>01_004</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>https://shopee.vn/hoangphucinternational</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>https://shopee.vn/product/36464652/51659909791</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Trang shop ngày 2026-09-27: 101 sản phẩm, 181,3k follower, 55,6k ratings, phản hồi 100%, Joined 9 Years Ago, có voucher.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>01_005</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>https://shopee.vn/locknlockvn</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>https://shopee.vn/product/55771655/4278889900</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Trang shop ngày 2026-09-27: 552 sản phẩm, 1,6m follower, 711,8k ratings, phản hồi 100%, Joined 9 Years Ago, có voucher.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>01_006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>https://shopee.vn/ugreen.vn</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>https://shopee.vn/Ugreen-4K60hz-6-IN-1USB-C-Tr%E1%BA%A1m-Docking-%C4%91a-ch%E1%BB%A9c-n%C4%83ng-USB3.2-Gen2-10Gbps-cho-iPad-Air-M2-11-13-''-2024-MacBook-Pro-M3-M2-M1-M4-MacBook-Air-M3-M2-M1-M4-HDMI-2xUSB-A-3.2-2xUSB-C-i.325696535.28707673838</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 1,1k sản phẩm, 694,9k follower, 279,6k ratings; 6 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>01_007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>https://shopee.vn/bama.bag</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>https://shopee.vn/Balo-nam-n%E1%BB%AF-%C4%91i-h%E1%BB%8Dc-%C4%91i-l%C3%A0m-BAMA-Solid-Backpack-ch%E1%BB%91ng-n%C6%B0%E1%BB%9Bc-nhi%E1%BB%81u-ng%C4%83n-%C4%91%E1%BB%B1ng-laptop-13-14-15.6-inch-i.63351086.40561859379</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 130 sản phẩm, 330,2k follower, 47,2k ratings; 8 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>01_008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>https://shopee.vn/lelananhpqwo87351</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>https://shopee.vn/M%C3%A1y-T%C4%83m-N%C6%B0%E1%BB%9Bc-C%E1%BA%A7m-Tay-Smart-Gadgets-T%C4%83m-N%C6%B0%E1%BB%9Bc-V%E1%BB%87-Sinh-R%C4%83ng-Mi%E1%BB%87ng-H%C3%A0ng-Ch%C3%ADnh-H%C3%A3ng-i.723523606.28401883528</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 37 sản phẩm, 1,2k follower, 8,9k ratings; 5 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>01_009</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>https://shopee.vn/giadungviet_123</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>https://shopee.vn/B%C3%A0n-%E1%BB%A6i-H%C6%A1i-N%C6%B0%E1%BB%9Bc-Mini-C%E1%BA%A7m-Tay-B%C3%A0n-l%C3%A0-H%C6%A1i-N%C6%B0%E1%BB%9Bc-Du-L%E1%BB%8Bch-C%C3%B4ng-Su%E1%BA%A5t-33W-Nh%E1%BB%8F-G%E1%BB%8Dn-Ti%E1%BB%87n-D%E1%BB%A5ng-D%E1%BB%85-D%C3%A0ng-G%E1%BA%A5p-G%E1%BB%8Dn-New-i.543219209.29156566589</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 52 sản phẩm, 10,2k follower, 10k ratings; 5 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>01_010</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>https://shopee.vn/shopmegold1</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>https://shopee.vn/B%E1%BB%99t-Ch%E1%BA%A5t-T%E1%BA%A9y-C%E1%BA%B7n-Axit-Chanh-d%C3%A0nh-cho-b%C3%ACnh-%C4%91un-%E1%BA%A5m-n%C6%B0%E1%BB%9Bc-B%E1%BB%99t-t%E1%BA%A9y-Canxi-t%E1%BA%A9y-b%C3%ACnh-%E1%BA%A5m-%C4%91un-n%C6%B0%E1%BB%9Bc-i.503004616.43953087993</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 762 sản phẩm, 131,1k follower, 471,8k ratings; 5 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>01_011</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>https://shopee.vn/delivietnam</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>https://shopee.vn/B%C3%BAt-highlight-Deli-25-m%C3%A0u-%C4%91%C3%A1nh-d%E1%BA%A5u-nh%E1%BB%9B-d%C3%B2ng-d%E1%BA%A1-quang-Deli-m%C3%A0u-pastel-neon-cho-h%E1%BB%8Dc-sinh-i.127805122.11115991321</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 1,8k sản phẩm, 1,9m follower, 2,4m ratings; 8 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>01_012</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>https://shopee.vn/techzoneaudio</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>https://shopee.vn/Loa-bluetooth-Kh%C3%B4ng-D%C3%A2y-HM-867-Thi%E1%BA%BFt-K%E1%BA%BF-Nh%E1%BB%8F-G%E1%BB%8Dn-Ti%E1%BB%87n-D%E1%BB%A5ng-D%E1%BB%85-S%E1%BB%AD-D%E1%BB%A5ng-REMI-OFFICIAL-i.740144125.25026374958</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 40 sản phẩm, 6,1k follower, 9,7k ratings; 4 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>01_013</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>https://shopee.vn/tz_speaker</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>https://shopee.vn/Loa-Bluetooth-HM-805-Loa-Kh%C3%B4ng-D%C3%A2y-Th%C3%B4ng-Minh-Led-%C3%82m-Thanh-Ch%C3%ADnh-H%C3%A3ng-i.741155619.29703640124</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 31 sản phẩm, 1,4k follower, 6,4k ratings; 4 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>01_014</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>https://shopee.vn/minhphatprinting</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>https://shopee.vn/ALBUM-%C4%90%E1%BB%B0NG-200-T%E1%BA%A4M-%E1%BA%A2NH-6x9-i.149595849.9285361629</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 80 sản phẩm, 52k follower, 50,6k ratings; 7 Years Ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>01_015</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>https://shopee.vn/topick_global</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>https://shopee.vn/M%E1%BA%B7t-n%E1%BA%A1-m%E1%BA%AFt-l%E1%BB%A5a-m%C3%B4-ph%E1%BB%8Fng-hai-m%E1%BA%B7t-m%E1%BA%B7t-n%E1%BA%A1-m%E1%BA%AFt-b%C3%B3ng-r%C3%A2m-tho%C3%A1ng-kh%C3%AD-tho%E1%BA%A3i-m%C3%A1i-qu%C3%A0-t%E1%BA%B7ng-nhi%E1%BB%81u-m%C3%A0u-unisex-b%E1%BB%8Dc-n%E1%BA%A1-m%E1%BA%AFt-ng%E1%BB%A7-d%C3%A0nh-cho-h%E1%BB%8Dc-sinh-Thi%E1%BA%BFt-b%E1%BB%8B-b%E1%BA%A3o-v%E1%BB%87-m%E1%BA%A5t-%C4%91i%E1%BB%87n-n%E1%BB%ADa-%C4%91%C3%AAm-i.196261835.24974349815</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Trang shop quan sát 2026-09-28; sản phẩm và review của shop chưa đủ 5 sản phẩm × 10 review. 324,3k sản phẩm, 5,5m follower, 7,3m ratings; 7 Years Ago.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
